--- a/Laporan Buku Tamu.xlsx
+++ b/Laporan Buku Tamu.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>No</t>
   </si>
@@ -87,6 +87,24 @@
   </si>
   <si>
     <t>ada je</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>raffki</t>
+  </si>
+  <si>
+    <t>Jl.Kaki</t>
+  </si>
+  <si>
+    <t>081365674580</t>
+  </si>
+  <si>
+    <t>fikrr</t>
+  </si>
+  <si>
+    <t>ada kerjasama bisnis orangkaya</t>
   </si>
 </sst>
 </file>
@@ -426,7 +444,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -519,6 +537,29 @@
       </c>
       <c r="G4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
